--- a/src/components/Accomodation/Accomodation.xlsx
+++ b/src/components/Accomodation/Accomodation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Room No</t>
   </si>
@@ -40,10 +40,25 @@
     <t>AC/Non AC</t>
   </si>
   <si>
-    <t>Begin</t>
-  </si>
-  <si>
-    <t>End</t>
+    <t>Check-in</t>
+  </si>
+  <si>
+    <t>Check-out</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per Room per Day </t>
+  </si>
+  <si>
+    <t>Room Type</t>
+  </si>
+  <si>
+    <t>Extra Bed Provided</t>
+  </si>
+  <si>
+    <t>No. of Days Rented</t>
   </si>
   <si>
     <t>Krishna Kishore Julakanti</t>
@@ -61,6 +76,9 @@
     <t>AC</t>
   </si>
   <si>
+    <t>3 bed</t>
+  </si>
+  <si>
     <t>Kiranmai Pola</t>
   </si>
   <si>
@@ -71,6 +89,21 @@
   </si>
   <si>
     <t>Non AC</t>
+  </si>
+  <si>
+    <t>2 bed</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Gopalkrishna</t>
+  </si>
+  <si>
+    <t>Vivek</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -80,10 +113,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d mmm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -107,14 +146,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -371,55 +413,126 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>101.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3">
         <v>46174.0</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>46179.0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1000.0</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>102.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3">
         <v>46175.0</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="3">
         <v>46178.0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>200.0</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3">
+        <v>46174.0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>46179.0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>2300.0</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/components/Accomodation/Accomodation.xlsx
+++ b/src/components/Accomodation/Accomodation.xlsx
@@ -49,7 +49,7 @@
     <t>Floor</t>
   </si>
   <si>
-    <t xml:space="preserve">Cost per Room per Day </t>
+    <t>Cost per Room per Day</t>
   </si>
   <si>
     <t>Room Type</t>
